--- a/main/ig/ValueSet-input-tddui-task-prestation-valueset.xlsx
+++ b/main/ig/ValueSet-input-tddui-task-prestation-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T09:58:03+00:00</t>
+    <t>2026-01-26T12:56:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-input-tddui-task-prestation-valueset.xlsx
+++ b/main/ig/ValueSet-input-tddui-task-prestation-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T12:56:49+00:00</t>
+    <t>2026-02-05T13:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-input-tddui-task-prestation-valueset.xlsx
+++ b/main/ig/ValueSet-input-tddui-task-prestation-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T13:38:35+00:00</t>
+    <t>2026-02-05T14:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
